--- a/funding/CPL_Funding_Model_2026.xlsx
+++ b/funding/CPL_Funding_Model_2026.xlsx
@@ -238,7 +238,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -371,6 +371,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P129"/>
+  <dimension ref="A2:P130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="4.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -1048,7 +1051,7 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>SUM(C9:C126)</f>
+        <f>SUM(C9:C127)</f>
         <v/>
       </c>
       <c r="D8" s="24">
@@ -1234,7 +1237,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>Chabot Hayward</t>
+          <t>Chabot</t>
         </is>
       </c>
       <c r="C11" s="31" t="n">
@@ -3625,79 +3628,78 @@
       <c r="P48" s="51" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="29" t="n">
-        <v>80</v>
-      </c>
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>Pasadena</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="n">
-        <v>33670</v>
-      </c>
-      <c r="D49" s="50">
+      <c r="A49" t="n">
+        <v>119</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mt San Antonio Noncredit</t>
+        </is>
+      </c>
+      <c r="C49" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="53">
         <f>C49/C$8</f>
         <v/>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="52">
         <f>$D49*E$7*$H$3</f>
         <v/>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="52">
         <f>C49*F$7</f>
         <v/>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="52">
         <f>$D49*G$7*$H$3</f>
         <v/>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="52">
         <f>C49*H$7</f>
         <v/>
       </c>
-      <c r="I49" s="31">
+      <c r="I49" s="52">
         <f>$D49*I$7*$H$3</f>
         <v/>
       </c>
-      <c r="J49" s="31">
+      <c r="J49" s="52">
         <f>C49*J$7</f>
         <v/>
       </c>
-      <c r="K49" s="41">
+      <c r="K49" s="52">
         <f>E49+G49+I49</f>
         <v/>
       </c>
-      <c r="L49" s="30" t="inlineStr">
-        <is>
-          <t>Pasadena Area Community College District</t>
-        </is>
-      </c>
-      <c r="M49" s="30" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Mt. San Antonio Community College District</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="N49" s="34" t="n">
+      <c r="N49" t="n">
         <v>1200796</v>
       </c>
-      <c r="O49" s="35">
+      <c r="O49" s="54">
         <f>N49/N$8</f>
         <v/>
       </c>
-      <c r="P49" s="51" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="29" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B50" s="30" t="inlineStr">
         <is>
-          <t>Rio Hondo</t>
+          <t>Pasadena</t>
         </is>
       </c>
       <c r="C50" s="31" t="n">
-        <v>28241</v>
+        <v>33670</v>
       </c>
       <c r="D50" s="50">
         <f>C50/C$8</f>
@@ -3733,7 +3735,7 @@
       </c>
       <c r="L50" s="30" t="inlineStr">
         <is>
-          <t>Rio Hondo Community College District</t>
+          <t>Pasadena Area Community College District</t>
         </is>
       </c>
       <c r="M50" s="30" t="inlineStr">
@@ -3752,15 +3754,15 @@
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="29" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B51" s="30" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Rio Hondo</t>
         </is>
       </c>
       <c r="C51" s="31" t="n">
-        <v>37289</v>
+        <v>28241</v>
       </c>
       <c r="D51" s="50">
         <f>C51/C$8</f>
@@ -3796,7 +3798,7 @@
       </c>
       <c r="L51" s="30" t="inlineStr">
         <is>
-          <t>Santa Monica Community College District</t>
+          <t>Rio Hondo Community College District</t>
         </is>
       </c>
       <c r="M51" s="30" t="inlineStr">
@@ -3815,15 +3817,15 @@
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="29" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B52" s="30" t="inlineStr">
         <is>
-          <t>West LA</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="C52" s="31" t="n">
-        <v>18347</v>
+        <v>37289</v>
       </c>
       <c r="D52" s="50">
         <f>C52/C$8</f>
@@ -3859,7 +3861,7 @@
       </c>
       <c r="L52" s="30" t="inlineStr">
         <is>
-          <t>Los Angeles Community College District</t>
+          <t>Santa Monica Community College District</t>
         </is>
       </c>
       <c r="M52" s="30" t="inlineStr">
@@ -3878,15 +3880,15 @@
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="29" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="B53" s="30" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>West LA</t>
         </is>
       </c>
       <c r="C53" s="31" t="n">
-        <v>9464</v>
+        <v>18347</v>
       </c>
       <c r="D53" s="50">
         <f>C53/C$8</f>
@@ -3922,16 +3924,16 @@
       </c>
       <c r="L53" s="30" t="inlineStr">
         <is>
-          <t>State Center Community College District</t>
+          <t>Los Angeles Community College District</t>
         </is>
       </c>
       <c r="M53" s="30" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="N53" s="34" t="n">
-        <v>21685</v>
+        <v>1200796</v>
       </c>
       <c r="O53" s="35">
         <f>N53/N$8</f>
@@ -3941,15 +3943,15 @@
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="30" t="inlineStr">
         <is>
-          <t>Marin</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="C54" s="31" t="n">
-        <v>7996</v>
+        <v>9464</v>
       </c>
       <c r="D54" s="50">
         <f>C54/C$8</f>
@@ -3985,16 +3987,16 @@
       </c>
       <c r="L54" s="30" t="inlineStr">
         <is>
-          <t>Marin Community College District</t>
+          <t>State Center Community College District</t>
         </is>
       </c>
       <c r="M54" s="30" t="inlineStr">
         <is>
-          <t>Marin</t>
+          <t>Madera</t>
         </is>
       </c>
       <c r="N54" s="34" t="n">
-        <v>25654</v>
+        <v>21685</v>
       </c>
       <c r="O54" s="35">
         <f>N54/N$8</f>
@@ -4004,15 +4006,15 @@
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="30" t="inlineStr">
         <is>
-          <t>Mendocino</t>
+          <t>Marin</t>
         </is>
       </c>
       <c r="C55" s="31" t="n">
-        <v>6759</v>
+        <v>7996</v>
       </c>
       <c r="D55" s="50">
         <f>C55/C$8</f>
@@ -4048,16 +4050,16 @@
       </c>
       <c r="L55" s="30" t="inlineStr">
         <is>
-          <t>Mendocino-Lake Community College District</t>
+          <t>Marin Community College District</t>
         </is>
       </c>
       <c r="M55" s="30" t="inlineStr">
         <is>
-          <t>Mendocino</t>
+          <t>Marin</t>
         </is>
       </c>
       <c r="N55" s="34" t="n">
-        <v>18778</v>
+        <v>25654</v>
       </c>
       <c r="O55" s="35">
         <f>N55/N$8</f>
@@ -4067,15 +4069,15 @@
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="30" t="inlineStr">
         <is>
-          <t>Merced</t>
+          <t>Mendocino</t>
         </is>
       </c>
       <c r="C56" s="31" t="n">
-        <v>16625</v>
+        <v>6759</v>
       </c>
       <c r="D56" s="50">
         <f>C56/C$8</f>
@@ -4111,16 +4113,16 @@
       </c>
       <c r="L56" s="30" t="inlineStr">
         <is>
-          <t>Merced Community College District</t>
+          <t>Mendocino-Lake Community College District</t>
         </is>
       </c>
       <c r="M56" s="30" t="inlineStr">
         <is>
-          <t>Merced</t>
+          <t>Mendocino</t>
         </is>
       </c>
       <c r="N56" s="34" t="n">
-        <v>35277</v>
+        <v>18778</v>
       </c>
       <c r="O56" s="35">
         <f>N56/N$8</f>
@@ -4130,15 +4132,15 @@
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="29" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>Hartnell</t>
+          <t>Merced</t>
         </is>
       </c>
       <c r="C57" s="31" t="n">
-        <v>11903</v>
+        <v>16625</v>
       </c>
       <c r="D57" s="50">
         <f>C57/C$8</f>
@@ -4174,16 +4176,16 @@
       </c>
       <c r="L57" s="30" t="inlineStr">
         <is>
-          <t>Hartnell Community College District</t>
+          <t>Merced Community College District</t>
         </is>
       </c>
       <c r="M57" s="30" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Merced</t>
         </is>
       </c>
       <c r="N57" s="34" t="n">
-        <v>44526</v>
+        <v>35277</v>
       </c>
       <c r="O57" s="35">
         <f>N57/N$8</f>
@@ -4193,15 +4195,15 @@
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="29" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B58" s="30" t="inlineStr">
         <is>
-          <t>Monterey</t>
+          <t>Hartnell</t>
         </is>
       </c>
       <c r="C58" s="31" t="n">
-        <v>10592</v>
+        <v>11903</v>
       </c>
       <c r="D58" s="50">
         <f>C58/C$8</f>
@@ -4237,7 +4239,7 @@
       </c>
       <c r="L58" s="30" t="inlineStr">
         <is>
-          <t>Monterey Peninsula Community College District</t>
+          <t>Hartnell Community College District</t>
         </is>
       </c>
       <c r="M58" s="30" t="inlineStr">
@@ -4256,15 +4258,15 @@
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="29" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>Napa</t>
+          <t>Monterey</t>
         </is>
       </c>
       <c r="C59" s="31" t="n">
-        <v>6418</v>
+        <v>10592</v>
       </c>
       <c r="D59" s="50">
         <f>C59/C$8</f>
@@ -4300,16 +4302,16 @@
       </c>
       <c r="L59" s="30" t="inlineStr">
         <is>
-          <t>Napa Valley Community College District</t>
+          <t>Monterey Peninsula Community College District</t>
         </is>
       </c>
       <c r="M59" s="30" t="inlineStr">
         <is>
-          <t>Napa</t>
+          <t>Monterey</t>
         </is>
       </c>
       <c r="N59" s="34" t="n">
-        <v>16949</v>
+        <v>44526</v>
       </c>
       <c r="O59" s="35">
         <f>N59/N$8</f>
@@ -4319,15 +4321,15 @@
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="29" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B60" s="30" t="inlineStr">
         <is>
-          <t>Coastline</t>
+          <t>Napa</t>
         </is>
       </c>
       <c r="C60" s="31" t="n">
-        <v>16212</v>
+        <v>6418</v>
       </c>
       <c r="D60" s="50">
         <f>C60/C$8</f>
@@ -4363,16 +4365,16 @@
       </c>
       <c r="L60" s="30" t="inlineStr">
         <is>
-          <t>Coast Community College District</t>
+          <t>Napa Valley Community College District</t>
         </is>
       </c>
       <c r="M60" s="30" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Napa</t>
         </is>
       </c>
       <c r="N60" s="34" t="n">
-        <v>399262</v>
+        <v>16949</v>
       </c>
       <c r="O60" s="35">
         <f>N60/N$8</f>
@@ -4382,15 +4384,15 @@
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="29" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Coastline</t>
         </is>
       </c>
       <c r="C61" s="31" t="n">
-        <v>18788</v>
+        <v>16212</v>
       </c>
       <c r="D61" s="50">
         <f>C61/C$8</f>
@@ -4426,7 +4428,7 @@
       </c>
       <c r="L61" s="30" t="inlineStr">
         <is>
-          <t>North Orange County Community College District</t>
+          <t>Coast Community College District</t>
         </is>
       </c>
       <c r="M61" s="30" t="inlineStr">
@@ -4445,15 +4447,15 @@
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="29" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B62" s="30" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Cypress</t>
         </is>
       </c>
       <c r="C62" s="31" t="n">
-        <v>26433</v>
+        <v>18788</v>
       </c>
       <c r="D62" s="50">
         <f>C62/C$8</f>
@@ -4508,15 +4510,15 @@
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="29" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B63" s="30" t="inlineStr">
         <is>
-          <t>Golden West</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="C63" s="31" t="n">
-        <v>18058</v>
+        <v>26433</v>
       </c>
       <c r="D63" s="50">
         <f>C63/C$8</f>
@@ -4552,7 +4554,7 @@
       </c>
       <c r="L63" s="30" t="inlineStr">
         <is>
-          <t>Coast Community College District</t>
+          <t>North Orange County Community College District</t>
         </is>
       </c>
       <c r="M63" s="30" t="inlineStr">
@@ -4571,15 +4573,15 @@
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="29" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B64" s="30" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Golden West</t>
         </is>
       </c>
       <c r="C64" s="31" t="n">
-        <v>20375</v>
+        <v>18058</v>
       </c>
       <c r="D64" s="50">
         <f>C64/C$8</f>
@@ -4615,7 +4617,7 @@
       </c>
       <c r="L64" s="30" t="inlineStr">
         <is>
-          <t>South Orange County Community College District</t>
+          <t>Coast Community College District</t>
         </is>
       </c>
       <c r="M64" s="30" t="inlineStr">
@@ -4634,15 +4636,15 @@
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="29" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="B65" s="30" t="inlineStr">
         <is>
-          <t>North Orange Adult</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C65" s="31" t="n">
-        <v>16046</v>
+        <v>20375</v>
       </c>
       <c r="D65" s="50">
         <f>C65/C$8</f>
@@ -4678,7 +4680,7 @@
       </c>
       <c r="L65" s="30" t="inlineStr">
         <is>
-          <t>North Orange County Community College District</t>
+          <t>South Orange County Community College District</t>
         </is>
       </c>
       <c r="M65" s="30" t="inlineStr">
@@ -4697,15 +4699,15 @@
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="29" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B66" s="30" t="inlineStr">
         <is>
-          <t>Orange Coast</t>
+          <t>North Orange Adult</t>
         </is>
       </c>
       <c r="C66" s="31" t="n">
-        <v>22995</v>
+        <v>16046</v>
       </c>
       <c r="D66" s="50">
         <f>C66/C$8</f>
@@ -4741,7 +4743,7 @@
       </c>
       <c r="L66" s="30" t="inlineStr">
         <is>
-          <t>Coast Community College District</t>
+          <t>North Orange County Community College District</t>
         </is>
       </c>
       <c r="M66" s="30" t="inlineStr">
@@ -4760,15 +4762,15 @@
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="29" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>Saddleback</t>
+          <t>Orange Coast</t>
         </is>
       </c>
       <c r="C67" s="31" t="n">
-        <v>36459</v>
+        <v>22995</v>
       </c>
       <c r="D67" s="50">
         <f>C67/C$8</f>
@@ -4804,7 +4806,7 @@
       </c>
       <c r="L67" s="30" t="inlineStr">
         <is>
-          <t>South Orange County Community College District</t>
+          <t>Coast Community College District</t>
         </is>
       </c>
       <c r="M67" s="30" t="inlineStr">
@@ -4823,15 +4825,15 @@
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="29" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B68" s="30" t="inlineStr">
         <is>
-          <t>Santa Ana</t>
+          <t>Saddleback</t>
         </is>
       </c>
       <c r="C68" s="31" t="n">
-        <v>57847</v>
+        <v>36459</v>
       </c>
       <c r="D68" s="50">
         <f>C68/C$8</f>
@@ -4867,7 +4869,7 @@
       </c>
       <c r="L68" s="30" t="inlineStr">
         <is>
-          <t>Rancho Santiago Community College District</t>
+          <t>South Orange County Community College District</t>
         </is>
       </c>
       <c r="M68" s="30" t="inlineStr">
@@ -4886,15 +4888,15 @@
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="29" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B69" s="30" t="inlineStr">
         <is>
-          <t>Santiago Canyon</t>
+          <t>Santa Ana</t>
         </is>
       </c>
       <c r="C69" s="31" t="n">
-        <v>29707</v>
+        <v>57847</v>
       </c>
       <c r="D69" s="50">
         <f>C69/C$8</f>
@@ -4949,15 +4951,15 @@
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="29" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B70" s="30" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Santiago Canyon</t>
         </is>
       </c>
       <c r="C70" s="31" t="n">
-        <v>24187</v>
+        <v>29707</v>
       </c>
       <c r="D70" s="50">
         <f>C70/C$8</f>
@@ -4993,16 +4995,16 @@
       </c>
       <c r="L70" s="30" t="inlineStr">
         <is>
-          <t>Sierra Joint Community College District</t>
+          <t>Rancho Santiago Community College District</t>
         </is>
       </c>
       <c r="M70" s="30" t="inlineStr">
         <is>
-          <t>Placer</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="N70" s="34" t="n">
-        <v>71637</v>
+        <v>399262</v>
       </c>
       <c r="O70" s="35">
         <f>N70/N$8</f>
@@ -5012,15 +5014,15 @@
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="29" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="B71" s="30" t="inlineStr">
         <is>
-          <t>Feather River</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="C71" s="31" t="n">
-        <v>2739</v>
+        <v>24187</v>
       </c>
       <c r="D71" s="50">
         <f>C71/C$8</f>
@@ -5056,18 +5058,16 @@
       </c>
       <c r="L71" s="30" t="inlineStr">
         <is>
-          <t>Feather River Community College District</t>
+          <t>Sierra Joint Community College District</t>
         </is>
       </c>
       <c r="M71" s="30" t="inlineStr">
         <is>
-          <t>Plumas</t>
-        </is>
-      </c>
-      <c r="N71" s="37" t="inlineStr">
-        <is>
-          <t>N/A*</t>
-        </is>
+          <t>Placer</t>
+        </is>
+      </c>
+      <c r="N71" s="34" t="n">
+        <v>71637</v>
       </c>
       <c r="O71" s="35">
         <f>N71/N$8</f>
@@ -5077,15 +5077,15 @@
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="29" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B72" s="30" t="inlineStr">
         <is>
-          <t>Desert</t>
+          <t>Feather River</t>
         </is>
       </c>
       <c r="C72" s="31" t="n">
-        <v>16556</v>
+        <v>2739</v>
       </c>
       <c r="D72" s="50">
         <f>C72/C$8</f>
@@ -5121,16 +5121,18 @@
       </c>
       <c r="L72" s="30" t="inlineStr">
         <is>
-          <t>Desert Community College District</t>
+          <t>Feather River Community College District</t>
         </is>
       </c>
       <c r="M72" s="30" t="inlineStr">
         <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="N72" s="34" t="n">
-        <v>378406</v>
+          <t>Plumas</t>
+        </is>
+      </c>
+      <c r="N72" s="37" t="inlineStr">
+        <is>
+          <t>N/A*</t>
+        </is>
       </c>
       <c r="O72" s="35">
         <f>N72/N$8</f>
@@ -5140,15 +5142,15 @@
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="29" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="B73" s="30" t="inlineStr">
         <is>
-          <t>Moreno Valley</t>
+          <t>Desert</t>
         </is>
       </c>
       <c r="C73" s="31" t="n">
-        <v>15460</v>
+        <v>16556</v>
       </c>
       <c r="D73" s="50">
         <f>C73/C$8</f>
@@ -5184,7 +5186,7 @@
       </c>
       <c r="L73" s="30" t="inlineStr">
         <is>
-          <t>Riverside Community College District</t>
+          <t>Desert Community College District</t>
         </is>
       </c>
       <c r="M73" s="30" t="inlineStr">
@@ -5203,15 +5205,15 @@
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="29" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B74" s="30" t="inlineStr">
         <is>
-          <t>Mt. San Jacinto</t>
+          <t>Moreno Valley</t>
         </is>
       </c>
       <c r="C74" s="31" t="n">
-        <v>24319</v>
+        <v>15460</v>
       </c>
       <c r="D74" s="50">
         <f>C74/C$8</f>
@@ -5247,7 +5249,7 @@
       </c>
       <c r="L74" s="30" t="inlineStr">
         <is>
-          <t>Mt. San Jacinto Community College District</t>
+          <t>Riverside Community College District</t>
         </is>
       </c>
       <c r="M74" s="30" t="inlineStr">
@@ -5266,15 +5268,15 @@
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="29" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B75" s="30" t="inlineStr">
         <is>
-          <t>Norco College</t>
+          <t>Mt. San Jacinto</t>
         </is>
       </c>
       <c r="C75" s="31" t="n">
-        <v>15897</v>
+        <v>24319</v>
       </c>
       <c r="D75" s="50">
         <f>C75/C$8</f>
@@ -5310,7 +5312,7 @@
       </c>
       <c r="L75" s="30" t="inlineStr">
         <is>
-          <t>Riverside Community College District</t>
+          <t>Mt. San Jacinto Community College District</t>
         </is>
       </c>
       <c r="M75" s="30" t="inlineStr">
@@ -5329,15 +5331,15 @@
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="29" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B76" s="30" t="inlineStr">
         <is>
-          <t>Palo Verde</t>
+          <t>Norco College</t>
         </is>
       </c>
       <c r="C76" s="31" t="n">
-        <v>6472</v>
+        <v>15897</v>
       </c>
       <c r="D76" s="50">
         <f>C76/C$8</f>
@@ -5373,7 +5375,7 @@
       </c>
       <c r="L76" s="30" t="inlineStr">
         <is>
-          <t>Palo Verde Community College District</t>
+          <t>Riverside Community College District</t>
         </is>
       </c>
       <c r="M76" s="30" t="inlineStr">
@@ -5392,15 +5394,15 @@
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="29" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B77" s="30" t="inlineStr">
         <is>
-          <t>Riverside</t>
+          <t>Palo Verde</t>
         </is>
       </c>
       <c r="C77" s="31" t="n">
-        <v>29205</v>
+        <v>6472</v>
       </c>
       <c r="D77" s="50">
         <f>C77/C$8</f>
@@ -5436,7 +5438,7 @@
       </c>
       <c r="L77" s="30" t="inlineStr">
         <is>
-          <t>Riverside Community College District</t>
+          <t>Palo Verde Community College District</t>
         </is>
       </c>
       <c r="M77" s="30" t="inlineStr">
@@ -5455,15 +5457,15 @@
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="29" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="B78" s="30" t="inlineStr">
         <is>
-          <t>American River</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="C78" s="31" t="n">
-        <v>42226</v>
+        <v>29205</v>
       </c>
       <c r="D78" s="50">
         <f>C78/C$8</f>
@@ -5499,16 +5501,16 @@
       </c>
       <c r="L78" s="30" t="inlineStr">
         <is>
-          <t>Los Rios Community College District</t>
+          <t>Riverside Community College District</t>
         </is>
       </c>
       <c r="M78" s="30" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Riverside</t>
         </is>
       </c>
       <c r="N78" s="34" t="n">
-        <v>257597</v>
+        <v>378406</v>
       </c>
       <c r="O78" s="35">
         <f>N78/N$8</f>
@@ -5518,15 +5520,15 @@
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="29" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B79" s="30" t="inlineStr">
         <is>
-          <t>Cosumnes River</t>
+          <t>American River</t>
         </is>
       </c>
       <c r="C79" s="31" t="n">
-        <v>20682</v>
+        <v>42226</v>
       </c>
       <c r="D79" s="50">
         <f>C79/C$8</f>
@@ -5581,15 +5583,15 @@
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="29" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B80" s="30" t="inlineStr">
         <is>
-          <t>Folsom Lake</t>
+          <t>Cosumnes River</t>
         </is>
       </c>
       <c r="C80" s="31" t="n">
-        <v>14208</v>
+        <v>20682</v>
       </c>
       <c r="D80" s="50">
         <f>C80/C$8</f>
@@ -5644,15 +5646,15 @@
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="29" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B81" s="30" t="inlineStr">
         <is>
-          <t>Sacramento City</t>
+          <t>Folsom Lake</t>
         </is>
       </c>
       <c r="C81" s="31" t="n">
-        <v>28012</v>
+        <v>14208</v>
       </c>
       <c r="D81" s="50">
         <f>C81/C$8</f>
@@ -5707,15 +5709,15 @@
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="29" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B82" s="30" t="inlineStr">
         <is>
-          <t>Barstow</t>
+          <t>Sacramento City</t>
         </is>
       </c>
       <c r="C82" s="31" t="n">
-        <v>5274</v>
+        <v>28012</v>
       </c>
       <c r="D82" s="50">
         <f>C82/C$8</f>
@@ -5751,16 +5753,16 @@
       </c>
       <c r="L82" s="30" t="inlineStr">
         <is>
-          <t>Barstow Community College District</t>
+          <t>Los Rios Community College District</t>
         </is>
       </c>
       <c r="M82" s="30" t="inlineStr">
         <is>
-          <t>San Bernardino</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="N82" s="34" t="n">
-        <v>311528</v>
+        <v>257597</v>
       </c>
       <c r="O82" s="35">
         <f>N82/N$8</f>
@@ -5770,15 +5772,15 @@
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B83" s="30" t="inlineStr">
         <is>
-          <t>Chaffey</t>
+          <t>Barstow</t>
         </is>
       </c>
       <c r="C83" s="31" t="n">
-        <v>30505</v>
+        <v>5274</v>
       </c>
       <c r="D83" s="50">
         <f>C83/C$8</f>
@@ -5814,7 +5816,7 @@
       </c>
       <c r="L83" s="30" t="inlineStr">
         <is>
-          <t>Chaffey Community College District</t>
+          <t>Barstow Community College District</t>
         </is>
       </c>
       <c r="M83" s="30" t="inlineStr">
@@ -5833,15 +5835,15 @@
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="29" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B84" s="30" t="inlineStr">
         <is>
-          <t>Copper Mountain</t>
+          <t>Chaffey</t>
         </is>
       </c>
       <c r="C84" s="31" t="n">
-        <v>2278</v>
+        <v>30505</v>
       </c>
       <c r="D84" s="50">
         <f>C84/C$8</f>
@@ -5877,7 +5879,7 @@
       </c>
       <c r="L84" s="30" t="inlineStr">
         <is>
-          <t>Copper Mountain Community College District</t>
+          <t>Chaffey Community College District</t>
         </is>
       </c>
       <c r="M84" s="30" t="inlineStr">
@@ -5896,15 +5898,15 @@
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B85" s="30" t="inlineStr">
         <is>
-          <t>Crafton Hills</t>
+          <t>Copper Mountain</t>
         </is>
       </c>
       <c r="C85" s="31" t="n">
-        <v>7609</v>
+        <v>2278</v>
       </c>
       <c r="D85" s="50">
         <f>C85/C$8</f>
@@ -5940,7 +5942,7 @@
       </c>
       <c r="L85" s="30" t="inlineStr">
         <is>
-          <t>San Bernardino Community College District</t>
+          <t>Copper Mountain Community College District</t>
         </is>
       </c>
       <c r="M85" s="30" t="inlineStr">
@@ -5959,15 +5961,15 @@
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="29" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="B86" s="30" t="inlineStr">
         <is>
-          <t>San Bernardino</t>
+          <t>Crafton Hills</t>
         </is>
       </c>
       <c r="C86" s="31" t="n">
-        <v>16682</v>
+        <v>7609</v>
       </c>
       <c r="D86" s="50">
         <f>C86/C$8</f>
@@ -6022,15 +6024,15 @@
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="29" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
-          <t>Victor Valley</t>
+          <t>San Bernardino</t>
         </is>
       </c>
       <c r="C87" s="31" t="n">
-        <v>18646</v>
+        <v>16682</v>
       </c>
       <c r="D87" s="50">
         <f>C87/C$8</f>
@@ -6066,7 +6068,7 @@
       </c>
       <c r="L87" s="30" t="inlineStr">
         <is>
-          <t>Victor Valley Community College District</t>
+          <t>San Bernardino Community College District</t>
         </is>
       </c>
       <c r="M87" s="30" t="inlineStr">
@@ -6085,15 +6087,15 @@
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="29" t="n">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="B88" s="30" t="inlineStr">
         <is>
-          <t>Cuyamaca</t>
+          <t>Victor Valley</t>
         </is>
       </c>
       <c r="C88" s="31" t="n">
-        <v>12863</v>
+        <v>18646</v>
       </c>
       <c r="D88" s="50">
         <f>C88/C$8</f>
@@ -6129,16 +6131,16 @@
       </c>
       <c r="L88" s="30" t="inlineStr">
         <is>
-          <t>Grossmont-Cuyamaca Community College District</t>
+          <t>Victor Valley Community College District</t>
         </is>
       </c>
       <c r="M88" s="30" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Bernardino</t>
         </is>
       </c>
       <c r="N88" s="34" t="n">
-        <v>468583</v>
+        <v>311528</v>
       </c>
       <c r="O88" s="35">
         <f>N88/N$8</f>
@@ -6148,15 +6150,15 @@
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="29" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B89" s="30" t="inlineStr">
         <is>
-          <t>Grossmont</t>
+          <t>Cuyamaca</t>
         </is>
       </c>
       <c r="C89" s="31" t="n">
-        <v>18720</v>
+        <v>12863</v>
       </c>
       <c r="D89" s="50">
         <f>C89/C$8</f>
@@ -6211,15 +6213,15 @@
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="29" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B90" s="30" t="inlineStr">
         <is>
-          <t>MiraCosta</t>
+          <t>Grossmont</t>
         </is>
       </c>
       <c r="C90" s="31" t="n">
-        <v>20240</v>
+        <v>18720</v>
       </c>
       <c r="D90" s="50">
         <f>C90/C$8</f>
@@ -6255,7 +6257,7 @@
       </c>
       <c r="L90" s="30" t="inlineStr">
         <is>
-          <t>MiraCosta Community College District</t>
+          <t>Grossmont-Cuyamaca Community College District</t>
         </is>
       </c>
       <c r="M90" s="30" t="inlineStr">
@@ -6274,15 +6276,15 @@
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="29" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
-          <t>Palomar</t>
+          <t>MiraCosta</t>
         </is>
       </c>
       <c r="C91" s="31" t="n">
-        <v>27744</v>
+        <v>20240</v>
       </c>
       <c r="D91" s="50">
         <f>C91/C$8</f>
@@ -6318,7 +6320,7 @@
       </c>
       <c r="L91" s="30" t="inlineStr">
         <is>
-          <t>Palomar Community College District</t>
+          <t>MiraCosta Community College District</t>
         </is>
       </c>
       <c r="M91" s="30" t="inlineStr">
@@ -6337,15 +6339,15 @@
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="29" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B92" s="30" t="inlineStr">
         <is>
-          <t>San Diego Adult</t>
+          <t>Palomar</t>
         </is>
       </c>
       <c r="C92" s="31" t="n">
-        <v>22103</v>
+        <v>27744</v>
       </c>
       <c r="D92" s="50">
         <f>C92/C$8</f>
@@ -6381,7 +6383,7 @@
       </c>
       <c r="L92" s="30" t="inlineStr">
         <is>
-          <t>San Diego Community College District</t>
+          <t>Palomar Community College District</t>
         </is>
       </c>
       <c r="M92" s="30" t="inlineStr">
@@ -6400,15 +6402,15 @@
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="29" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="30" t="inlineStr">
         <is>
-          <t>San Diego City</t>
+          <t>San Diego Adult</t>
         </is>
       </c>
       <c r="C93" s="31" t="n">
-        <v>20155</v>
+        <v>22103</v>
       </c>
       <c r="D93" s="50">
         <f>C93/C$8</f>
@@ -6463,15 +6465,15 @@
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="29" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="30" t="inlineStr">
         <is>
-          <t>San Diego Mesa</t>
+          <t>San Diego City</t>
         </is>
       </c>
       <c r="C94" s="31" t="n">
-        <v>29045</v>
+        <v>20155</v>
       </c>
       <c r="D94" s="50">
         <f>C94/C$8</f>
@@ -6526,15 +6528,15 @@
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="29" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="30" t="inlineStr">
         <is>
-          <t>San Diego Miramar</t>
+          <t>San Diego Mesa</t>
         </is>
       </c>
       <c r="C95" s="31" t="n">
-        <v>21498</v>
+        <v>29045</v>
       </c>
       <c r="D95" s="50">
         <f>C95/C$8</f>
@@ -6589,15 +6591,15 @@
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="29" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B96" s="30" t="inlineStr">
         <is>
-          <t>Southwestern</t>
+          <t>San Diego Miramar</t>
         </is>
       </c>
       <c r="C96" s="31" t="n">
-        <v>25228</v>
+        <v>21498</v>
       </c>
       <c r="D96" s="50">
         <f>C96/C$8</f>
@@ -6633,7 +6635,7 @@
       </c>
       <c r="L96" s="30" t="inlineStr">
         <is>
-          <t>Southwestern Community College District</t>
+          <t>San Diego Community College District</t>
         </is>
       </c>
       <c r="M96" s="30" t="inlineStr">
@@ -6652,15 +6654,15 @@
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="29" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B97" s="30" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Southwestern</t>
         </is>
       </c>
       <c r="C97" s="31" t="n">
-        <v>39532</v>
+        <v>25228</v>
       </c>
       <c r="D97" s="50">
         <f>C97/C$8</f>
@@ -6696,16 +6698,16 @@
       </c>
       <c r="L97" s="30" t="inlineStr">
         <is>
-          <t>San Francisco Community College District</t>
+          <t>Southwestern Community College District</t>
         </is>
       </c>
       <c r="M97" s="30" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="N97" s="34" t="n">
-        <v>72403</v>
+        <v>468583</v>
       </c>
       <c r="O97" s="35">
         <f>N97/N$8</f>
@@ -6715,15 +6717,15 @@
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="29" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B98" s="30" t="inlineStr">
         <is>
-          <t>San Joaquin Delta</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="C98" s="31" t="n">
-        <v>23408</v>
+        <v>39532</v>
       </c>
       <c r="D98" s="50">
         <f>C98/C$8</f>
@@ -6759,16 +6761,16 @@
       </c>
       <c r="L98" s="30" t="inlineStr">
         <is>
-          <t>San Joaquin Delta Community College District</t>
+          <t>San Francisco Community College District</t>
         </is>
       </c>
       <c r="M98" s="30" t="inlineStr">
         <is>
-          <t>San Joaquin</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="N98" s="34" t="n">
-        <v>106683</v>
+        <v>72403</v>
       </c>
       <c r="O98" s="35">
         <f>N98/N$8</f>
@@ -6778,15 +6780,15 @@
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="29" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="B99" s="30" t="inlineStr">
         <is>
-          <t>Cuesta</t>
+          <t>San Joaquin Delta</t>
         </is>
       </c>
       <c r="C99" s="31" t="n">
-        <v>16728</v>
+        <v>23408</v>
       </c>
       <c r="D99" s="50">
         <f>C99/C$8</f>
@@ -6822,16 +6824,16 @@
       </c>
       <c r="L99" s="30" t="inlineStr">
         <is>
-          <t>San Luis Obispo County Community College District</t>
+          <t>San Joaquin Delta Community College District</t>
         </is>
       </c>
       <c r="M99" s="30" t="inlineStr">
         <is>
-          <t>San Luis Obispo</t>
+          <t>San Joaquin</t>
         </is>
       </c>
       <c r="N99" s="34" t="n">
-        <v>45711</v>
+        <v>106683</v>
       </c>
       <c r="O99" s="35">
         <f>N99/N$8</f>
@@ -6841,15 +6843,15 @@
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B100" s="30" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Cuesta</t>
         </is>
       </c>
       <c r="C100" s="31" t="n">
-        <v>9785</v>
+        <v>16728</v>
       </c>
       <c r="D100" s="50">
         <f>C100/C$8</f>
@@ -6885,16 +6887,16 @@
       </c>
       <c r="L100" s="30" t="inlineStr">
         <is>
-          <t>San Mateo County Community College District</t>
+          <t>San Luis Obispo County Community College District</t>
         </is>
       </c>
       <c r="M100" s="30" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>San Luis Obispo</t>
         </is>
       </c>
       <c r="N100" s="34" t="n">
-        <v>78896</v>
+        <v>45711</v>
       </c>
       <c r="O100" s="35">
         <f>N100/N$8</f>
@@ -6904,15 +6906,15 @@
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="29" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="B101" s="30" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C101" s="31" t="n">
-        <v>12930</v>
+        <v>9785</v>
       </c>
       <c r="D101" s="50">
         <f>C101/C$8</f>
@@ -6967,15 +6969,15 @@
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="29" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B102" s="30" t="inlineStr">
         <is>
-          <t>Skyline</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="C102" s="31" t="n">
-        <v>15497</v>
+        <v>12930</v>
       </c>
       <c r="D102" s="50">
         <f>C102/C$8</f>
@@ -7030,15 +7032,15 @@
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="29" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="B103" s="30" t="inlineStr">
         <is>
-          <t>Allan Hancock</t>
+          <t>Skyline</t>
         </is>
       </c>
       <c r="C103" s="31" t="n">
-        <v>18376</v>
+        <v>15497</v>
       </c>
       <c r="D103" s="50">
         <f>C103/C$8</f>
@@ -7074,16 +7076,16 @@
       </c>
       <c r="L103" s="30" t="inlineStr">
         <is>
-          <t>Allan Hancock Joint Community College District</t>
+          <t>San Mateo County Community College District</t>
         </is>
       </c>
       <c r="M103" s="30" t="inlineStr">
         <is>
-          <t>Santa Barbara</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="N103" s="34" t="n">
-        <v>54159</v>
+        <v>78896</v>
       </c>
       <c r="O103" s="35">
         <f>N103/N$8</f>
@@ -7093,15 +7095,15 @@
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="29" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="B104" s="30" t="inlineStr">
         <is>
-          <t>Santa Barbara</t>
+          <t>Allan Hancock</t>
         </is>
       </c>
       <c r="C104" s="31" t="n">
-        <v>25307</v>
+        <v>18376</v>
       </c>
       <c r="D104" s="50">
         <f>C104/C$8</f>
@@ -7137,7 +7139,7 @@
       </c>
       <c r="L104" s="30" t="inlineStr">
         <is>
-          <t>Santa Barbara Community College District</t>
+          <t>Allan Hancock Joint Community College District</t>
         </is>
       </c>
       <c r="M104" s="30" t="inlineStr">
@@ -7156,15 +7158,15 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="29" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B105" s="30" t="inlineStr">
         <is>
-          <t>Deanza</t>
+          <t>Santa Barbara</t>
         </is>
       </c>
       <c r="C105" s="31" t="n">
-        <v>27215</v>
+        <v>25307</v>
       </c>
       <c r="D105" s="50">
         <f>C105/C$8</f>
@@ -7200,16 +7202,16 @@
       </c>
       <c r="L105" s="30" t="inlineStr">
         <is>
-          <t>Foothill-De Anza Community College District</t>
+          <t>Santa Barbara Community College District</t>
         </is>
       </c>
       <c r="M105" s="30" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Santa Barbara</t>
         </is>
       </c>
       <c r="N105" s="34" t="n">
-        <v>171522</v>
+        <v>54159</v>
       </c>
       <c r="O105" s="35">
         <f>N105/N$8</f>
@@ -7219,15 +7221,15 @@
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="29" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B106" s="30" t="inlineStr">
         <is>
-          <t>Evergreen Valley</t>
+          <t>Deanza</t>
         </is>
       </c>
       <c r="C106" s="31" t="n">
-        <v>13401</v>
+        <v>27215</v>
       </c>
       <c r="D106" s="50">
         <f>C106/C$8</f>
@@ -7263,7 +7265,7 @@
       </c>
       <c r="L106" s="30" t="inlineStr">
         <is>
-          <t>San Jose-Evergreen Community College District</t>
+          <t>Foothill-De Anza Community College District</t>
         </is>
       </c>
       <c r="M106" s="30" t="inlineStr">
@@ -7282,15 +7284,15 @@
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="29" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B107" s="30" t="inlineStr">
         <is>
-          <t>Foothill</t>
+          <t>Evergreen Valley</t>
         </is>
       </c>
       <c r="C107" s="31" t="n">
-        <v>24888</v>
+        <v>13401</v>
       </c>
       <c r="D107" s="50">
         <f>C107/C$8</f>
@@ -7326,7 +7328,7 @@
       </c>
       <c r="L107" s="30" t="inlineStr">
         <is>
-          <t>Foothill-De Anza Community College District</t>
+          <t>San Jose-Evergreen Community College District</t>
         </is>
       </c>
       <c r="M107" s="30" t="inlineStr">
@@ -7345,15 +7347,15 @@
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="29" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B108" s="30" t="inlineStr">
         <is>
-          <t>Gavilan</t>
+          <t>Foothill</t>
         </is>
       </c>
       <c r="C108" s="31" t="n">
-        <v>8698</v>
+        <v>24888</v>
       </c>
       <c r="D108" s="50">
         <f>C108/C$8</f>
@@ -7389,7 +7391,7 @@
       </c>
       <c r="L108" s="30" t="inlineStr">
         <is>
-          <t>Gavilan Joint Community College District</t>
+          <t>Foothill-De Anza Community College District</t>
         </is>
       </c>
       <c r="M108" s="30" t="inlineStr">
@@ -7408,15 +7410,15 @@
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="29" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B109" s="30" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Gavilan</t>
         </is>
       </c>
       <c r="C109" s="31" t="n">
-        <v>11064</v>
+        <v>8698</v>
       </c>
       <c r="D109" s="50">
         <f>C109/C$8</f>
@@ -7452,7 +7454,7 @@
       </c>
       <c r="L109" s="30" t="inlineStr">
         <is>
-          <t>West Valley-Mission Community College District</t>
+          <t>Gavilan Joint Community College District</t>
         </is>
       </c>
       <c r="M109" s="30" t="inlineStr">
@@ -7471,15 +7473,15 @@
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="29" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="B110" s="30" t="inlineStr">
         <is>
-          <t>San Jose City</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="C110" s="31" t="n">
-        <v>13032</v>
+        <v>11064</v>
       </c>
       <c r="D110" s="50">
         <f>C110/C$8</f>
@@ -7515,7 +7517,7 @@
       </c>
       <c r="L110" s="30" t="inlineStr">
         <is>
-          <t>San Jose-Evergreen Community College District</t>
+          <t>West Valley-Mission Community College District</t>
         </is>
       </c>
       <c r="M110" s="30" t="inlineStr">
@@ -7534,15 +7536,15 @@
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="29" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B111" s="30" t="inlineStr">
         <is>
-          <t>West Valley</t>
+          <t>San Jose City</t>
         </is>
       </c>
       <c r="C111" s="31" t="n">
-        <v>12576</v>
+        <v>13032</v>
       </c>
       <c r="D111" s="50">
         <f>C111/C$8</f>
@@ -7578,7 +7580,7 @@
       </c>
       <c r="L111" s="30" t="inlineStr">
         <is>
-          <t>West Valley-Mission Community College District</t>
+          <t>San Jose-Evergreen Community College District</t>
         </is>
       </c>
       <c r="M111" s="30" t="inlineStr">
@@ -7597,15 +7599,15 @@
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="29" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="B112" s="30" t="inlineStr">
         <is>
-          <t>Cabrillo</t>
+          <t>West Valley</t>
         </is>
       </c>
       <c r="C112" s="31" t="n">
-        <v>14909</v>
+        <v>12576</v>
       </c>
       <c r="D112" s="50">
         <f>C112/C$8</f>
@@ -7641,16 +7643,16 @@
       </c>
       <c r="L112" s="30" t="inlineStr">
         <is>
-          <t>Cabrillo Community College District</t>
+          <t>West Valley-Mission Community College District</t>
         </is>
       </c>
       <c r="M112" s="30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="N112" s="34" t="n">
-        <v>36341</v>
+        <v>171522</v>
       </c>
       <c r="O112" s="35">
         <f>N112/N$8</f>
@@ -7660,15 +7662,15 @@
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="29" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B113" s="30" t="inlineStr">
         <is>
-          <t>Shasta</t>
+          <t>Cabrillo</t>
         </is>
       </c>
       <c r="C113" s="31" t="n">
-        <v>12424</v>
+        <v>14909</v>
       </c>
       <c r="D113" s="50">
         <f>C113/C$8</f>
@@ -7704,16 +7706,16 @@
       </c>
       <c r="L113" s="30" t="inlineStr">
         <is>
-          <t>Shasta-Tehama-Trinity Joint Community College District</t>
+          <t>Cabrillo Community College District</t>
         </is>
       </c>
       <c r="M113" s="30" t="inlineStr">
         <is>
-          <t>Shasta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="N113" s="34" t="n">
-        <v>40002</v>
+        <v>36341</v>
       </c>
       <c r="O113" s="35">
         <f>N113/N$8</f>
@@ -7723,15 +7725,15 @@
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="29" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B114" s="30" t="inlineStr">
         <is>
-          <t>Siskiyous</t>
+          <t>Shasta</t>
         </is>
       </c>
       <c r="C114" s="31" t="n">
-        <v>2837</v>
+        <v>12424</v>
       </c>
       <c r="D114" s="50">
         <f>C114/C$8</f>
@@ -7767,18 +7769,16 @@
       </c>
       <c r="L114" s="30" t="inlineStr">
         <is>
-          <t>Siskiyou Joint Community College District</t>
+          <t>Shasta-Tehama-Trinity Joint Community College District</t>
         </is>
       </c>
       <c r="M114" s="30" t="inlineStr">
         <is>
-          <t>Siskiyou</t>
-        </is>
-      </c>
-      <c r="N114" s="37" t="inlineStr">
-        <is>
-          <t>N/A*</t>
-        </is>
+          <t>Shasta</t>
+        </is>
+      </c>
+      <c r="N114" s="34" t="n">
+        <v>40002</v>
       </c>
       <c r="O114" s="35">
         <f>N114/N$8</f>
@@ -7788,15 +7788,15 @@
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="29" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B115" s="30" t="inlineStr">
         <is>
-          <t>Solano</t>
+          <t>Siskiyous</t>
         </is>
       </c>
       <c r="C115" s="31" t="n">
-        <v>12273</v>
+        <v>2837</v>
       </c>
       <c r="D115" s="50">
         <f>C115/C$8</f>
@@ -7832,16 +7832,18 @@
       </c>
       <c r="L115" s="30" t="inlineStr">
         <is>
-          <t>Solano County Community College District</t>
+          <t>Siskiyou Joint Community College District</t>
         </is>
       </c>
       <c r="M115" s="30" t="inlineStr">
         <is>
-          <t>Solano</t>
-        </is>
-      </c>
-      <c r="N115" s="34" t="n">
-        <v>77534</v>
+          <t>Siskiyou</t>
+        </is>
+      </c>
+      <c r="N115" s="37" t="inlineStr">
+        <is>
+          <t>N/A*</t>
+        </is>
       </c>
       <c r="O115" s="35">
         <f>N115/N$8</f>
@@ -7851,15 +7853,15 @@
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="29" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B116" s="30" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Solano</t>
         </is>
       </c>
       <c r="C116" s="31" t="n">
-        <v>30917</v>
+        <v>12273</v>
       </c>
       <c r="D116" s="50">
         <f>C116/C$8</f>
@@ -7895,16 +7897,16 @@
       </c>
       <c r="L116" s="30" t="inlineStr">
         <is>
-          <t>Sonoma County Junior College District</t>
+          <t>Solano County Community College District</t>
         </is>
       </c>
       <c r="M116" s="30" t="inlineStr">
         <is>
-          <t>Sonoma</t>
+          <t>Solano</t>
         </is>
       </c>
       <c r="N116" s="34" t="n">
-        <v>82997</v>
+        <v>77534</v>
       </c>
       <c r="O116" s="35">
         <f>N116/N$8</f>
@@ -7914,15 +7916,15 @@
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="29" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B117" s="30" t="inlineStr">
         <is>
-          <t>Modesto</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="C117" s="31" t="n">
-        <v>24685</v>
+        <v>30917</v>
       </c>
       <c r="D117" s="50">
         <f>C117/C$8</f>
@@ -7958,16 +7960,16 @@
       </c>
       <c r="L117" s="30" t="inlineStr">
         <is>
-          <t>Yosemite Community College District</t>
+          <t>Sonoma County Junior College District</t>
         </is>
       </c>
       <c r="M117" s="30" t="inlineStr">
         <is>
-          <t>Stanislaus</t>
+          <t>Sonoma</t>
         </is>
       </c>
       <c r="N117" s="34" t="n">
-        <v>81075</v>
+        <v>82997</v>
       </c>
       <c r="O117" s="35">
         <f>N117/N$8</f>
@@ -7977,15 +7979,15 @@
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="29" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="B118" s="30" t="inlineStr">
         <is>
-          <t>CalBright</t>
+          <t>Modesto</t>
         </is>
       </c>
       <c r="C118" s="31" t="n">
-        <v>2484</v>
+        <v>24685</v>
       </c>
       <c r="D118" s="50">
         <f>C118/C$8</f>
@@ -8019,20 +8021,20 @@
         <f>E118+G118+I118</f>
         <v/>
       </c>
-      <c r="L118" s="38" t="inlineStr">
-        <is>
-          <t>California Online Community College District</t>
-        </is>
-      </c>
-      <c r="M118" s="38" t="inlineStr">
-        <is>
-          <t>Statewide</t>
-        </is>
-      </c>
-      <c r="N118" s="39" t="n">
-        <v>5106199</v>
-      </c>
-      <c r="O118" s="40">
+      <c r="L118" s="30" t="inlineStr">
+        <is>
+          <t>Yosemite Community College District</t>
+        </is>
+      </c>
+      <c r="M118" s="30" t="inlineStr">
+        <is>
+          <t>Stanislaus</t>
+        </is>
+      </c>
+      <c r="N118" s="34" t="n">
+        <v>81075</v>
+      </c>
+      <c r="O118" s="35">
         <f>N118/N$8</f>
         <v/>
       </c>
@@ -8040,15 +8042,15 @@
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="29" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="B119" s="30" t="inlineStr">
         <is>
-          <t>Porterville</t>
+          <t>CalBright</t>
         </is>
       </c>
       <c r="C119" s="31" t="n">
-        <v>5751</v>
+        <v>2484</v>
       </c>
       <c r="D119" s="50">
         <f>C119/C$8</f>
@@ -8082,20 +8084,20 @@
         <f>E119+G119+I119</f>
         <v/>
       </c>
-      <c r="L119" s="30" t="inlineStr">
-        <is>
-          <t>Kern Community College District</t>
-        </is>
-      </c>
-      <c r="M119" s="30" t="inlineStr">
-        <is>
-          <t>Tulare</t>
-        </is>
-      </c>
-      <c r="N119" s="34" t="n">
-        <v>63560</v>
-      </c>
-      <c r="O119" s="35">
+      <c r="L119" s="38" t="inlineStr">
+        <is>
+          <t>California Online Community College District</t>
+        </is>
+      </c>
+      <c r="M119" s="38" t="inlineStr">
+        <is>
+          <t>Statewide</t>
+        </is>
+      </c>
+      <c r="N119" s="39" t="n">
+        <v>5106199</v>
+      </c>
+      <c r="O119" s="40">
         <f>N119/N$8</f>
         <v/>
       </c>
@@ -8103,15 +8105,15 @@
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="29" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="B120" s="30" t="inlineStr">
         <is>
-          <t>Sequoias</t>
+          <t>Porterville</t>
         </is>
       </c>
       <c r="C120" s="31" t="n">
-        <v>17376</v>
+        <v>5751</v>
       </c>
       <c r="D120" s="50">
         <f>C120/C$8</f>
@@ -8147,7 +8149,7 @@
       </c>
       <c r="L120" s="30" t="inlineStr">
         <is>
-          <t>Sequoias Community College District</t>
+          <t>Kern Community College District</t>
         </is>
       </c>
       <c r="M120" s="30" t="inlineStr">
@@ -8166,15 +8168,15 @@
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="29" t="n">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="B121" s="30" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Sequoias</t>
         </is>
       </c>
       <c r="C121" s="31" t="n">
-        <v>3786</v>
+        <v>17376</v>
       </c>
       <c r="D121" s="50">
         <f>C121/C$8</f>
@@ -8210,18 +8212,16 @@
       </c>
       <c r="L121" s="30" t="inlineStr">
         <is>
-          <t>Yosemite Community College District</t>
+          <t>Sequoias Community College District</t>
         </is>
       </c>
       <c r="M121" s="30" t="inlineStr">
         <is>
-          <t>Tuolumne</t>
-        </is>
-      </c>
-      <c r="N121" s="37" t="inlineStr">
-        <is>
-          <t>N/A*</t>
-        </is>
+          <t>Tulare</t>
+        </is>
+      </c>
+      <c r="N121" s="34" t="n">
+        <v>63560</v>
       </c>
       <c r="O121" s="35">
         <f>N121/N$8</f>
@@ -8231,15 +8231,15 @@
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="29" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B122" s="30" t="inlineStr">
         <is>
-          <t>Moorpark</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="C122" s="31" t="n">
-        <v>19597</v>
+        <v>3786</v>
       </c>
       <c r="D122" s="50">
         <f>C122/C$8</f>
@@ -8275,16 +8275,18 @@
       </c>
       <c r="L122" s="30" t="inlineStr">
         <is>
-          <t>Ventura County Community College District</t>
+          <t>Yosemite Community College District</t>
         </is>
       </c>
       <c r="M122" s="30" t="inlineStr">
         <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="N122" s="34" t="n">
-        <v>111435</v>
+          <t>Tuolumne</t>
+        </is>
+      </c>
+      <c r="N122" s="37" t="inlineStr">
+        <is>
+          <t>N/A*</t>
+        </is>
       </c>
       <c r="O122" s="35">
         <f>N122/N$8</f>
@@ -8294,15 +8296,15 @@
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="29" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B123" s="30" t="inlineStr">
         <is>
-          <t>Oxnard</t>
+          <t>Moorpark</t>
         </is>
       </c>
       <c r="C123" s="31" t="n">
-        <v>10620</v>
+        <v>19597</v>
       </c>
       <c r="D123" s="50">
         <f>C123/C$8</f>
@@ -8357,15 +8359,15 @@
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="29" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B124" s="30" t="inlineStr">
         <is>
-          <t>Ventura</t>
+          <t>Oxnard</t>
         </is>
       </c>
       <c r="C124" s="31" t="n">
-        <v>16543</v>
+        <v>10620</v>
       </c>
       <c r="D124" s="50">
         <f>C124/C$8</f>
@@ -8420,15 +8422,15 @@
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="29" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B125" s="30" t="inlineStr">
         <is>
-          <t>Woodland</t>
+          <t>Ventura</t>
         </is>
       </c>
       <c r="C125" s="31" t="n">
-        <v>6011</v>
+        <v>16543</v>
       </c>
       <c r="D125" s="50">
         <f>C125/C$8</f>
@@ -8464,16 +8466,16 @@
       </c>
       <c r="L125" s="30" t="inlineStr">
         <is>
-          <t>Yuba Community College District</t>
+          <t>Ventura County Community College District</t>
         </is>
       </c>
       <c r="M125" s="30" t="inlineStr">
         <is>
-          <t>Yolo</t>
+          <t>Ventura</t>
         </is>
       </c>
       <c r="N125" s="34" t="n">
-        <v>25523</v>
+        <v>111435</v>
       </c>
       <c r="O125" s="35">
         <f>N125/N$8</f>
@@ -8483,15 +8485,15 @@
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="29" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B126" s="30" t="inlineStr">
         <is>
-          <t>Yuba</t>
+          <t>Woodland</t>
         </is>
       </c>
       <c r="C126" s="31" t="n">
-        <v>8417</v>
+        <v>6011</v>
       </c>
       <c r="D126" s="50">
         <f>C126/C$8</f>
@@ -8532,11 +8534,11 @@
       </c>
       <c r="M126" s="30" t="inlineStr">
         <is>
-          <t>Yuba</t>
+          <t>Yolo</t>
         </is>
       </c>
       <c r="N126" s="34" t="n">
-        <v>14117</v>
+        <v>25523</v>
       </c>
       <c r="O126" s="35">
         <f>N126/N$8</f>
@@ -8545,26 +8547,89 @@
       <c r="P126" s="51" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1">
-      <c r="I127" s="41" t="inlineStr">
+      <c r="A127" s="29" t="n">
+        <v>117</v>
+      </c>
+      <c r="B127" s="30" t="inlineStr">
+        <is>
+          <t>Yuba</t>
+        </is>
+      </c>
+      <c r="C127" s="31" t="n">
+        <v>8417</v>
+      </c>
+      <c r="D127" s="50">
+        <f>C127/C$8</f>
+        <v/>
+      </c>
+      <c r="E127" s="31">
+        <f>$D127*E$7*$H$3</f>
+        <v/>
+      </c>
+      <c r="F127" s="31">
+        <f>C127*F$7</f>
+        <v/>
+      </c>
+      <c r="G127" s="31">
+        <f>$D127*G$7*$H$3</f>
+        <v/>
+      </c>
+      <c r="H127" s="31">
+        <f>C127*H$7</f>
+        <v/>
+      </c>
+      <c r="I127" s="31">
+        <f>$D127*I$7*$H$3</f>
+        <v/>
+      </c>
+      <c r="J127" s="31">
+        <f>C127*J$7</f>
+        <v/>
+      </c>
+      <c r="K127" s="41">
+        <f>E127+G127+I127</f>
+        <v/>
+      </c>
+      <c r="L127" s="30" t="inlineStr">
+        <is>
+          <t>Yuba Community College District</t>
+        </is>
+      </c>
+      <c r="M127" s="30" t="inlineStr">
+        <is>
+          <t>Yuba</t>
+        </is>
+      </c>
+      <c r="N127" s="34" t="n">
+        <v>14117</v>
+      </c>
+      <c r="O127" s="35">
+        <f>N127/N$8</f>
+        <v/>
+      </c>
+      <c r="P127" s="51" t="n"/>
+    </row>
+    <row r="128">
+      <c r="I128" s="41" t="inlineStr">
         <is>
           <t>AVERAGE ALLOCATION</t>
         </is>
       </c>
-      <c r="J127" s="45" t="n"/>
-      <c r="K127" s="41">
-        <f>AVERAGE(K9:K126)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="10" t="inlineStr">
+      <c r="J128" s="45" t="n"/>
+      <c r="K128" s="41">
+        <f>AVERAGE(K9:K127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>*Survey did not estimate counties &lt;65K in population</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="8" t="inlineStr">
+    <row r="130">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>Source: U.S. Census 2022 American Community Survey: https://data.census.gov/table/ACSDT1Y2022.B16010?q=Educational%20Attainment%20by%20employment%20status%20and%20state&amp;g=040XX00US06,06$0500000&amp;y=2022&amp;moe=false</t>
         </is>

--- a/funding/CPL_Funding_Model_2026.xlsx
+++ b/funding/CPL_Funding_Model_2026.xlsx
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="C48" s="31" t="n">
-        <v>66445</v>
+        <v>41950</v>
       </c>
       <c r="D48" s="50">
         <f>C48/C$8</f>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C49" s="52" t="n">
-        <v>0</v>
+        <v>35363</v>
       </c>
       <c r="D49" s="53">
         <f>C49/C$8</f>
@@ -8582,10 +8582,7 @@
         <f>$D127*I$7*$H$3</f>
         <v/>
       </c>
-      <c r="J127" s="31">
-        <f>C127*J$7</f>
-        <v/>
-      </c>
+      <c r="J127" s="45" t="n"/>
       <c r="K127" s="41">
         <f>E127+G127+I127</f>
         <v/>
